--- a/data/trans_bre/P19C07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,87</t>
+          <t>-2,6; 2,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,27</t>
+          <t>-2,99; 4,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 7,11</t>
+          <t>-1,37; 7,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 4,97</t>
+          <t>-7,89; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,0; 507,02</t>
+          <t>-99,99; 412,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,36; 279,21</t>
+          <t>-57,46; 229,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 218,38</t>
+          <t>-21,63; 229,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 171,21</t>
+          <t>-61,95; 154,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,02</t>
+          <t>-1,7; 3,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,52</t>
+          <t>-4,23; 0,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,51</t>
+          <t>-1,74; 2,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,76</t>
+          <t>-0,75; 4,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 211,74</t>
+          <t>-40,21; 186,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 20,62</t>
+          <t>-73,7; 30,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 225,72</t>
+          <t>-55,97; 244,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 222,24</t>
+          <t>-20,97; 220,02</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,45</t>
+          <t>-2,22; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,17</t>
+          <t>-1,24; 4,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,27</t>
+          <t>-3,01; 3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,45</t>
+          <t>-2,61; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 424,5</t>
+          <t>-78,63; 507,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,33; 328,11</t>
+          <t>-41,04; 314,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 202,75</t>
+          <t>-66,43; 153,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 183,55</t>
+          <t>-75,93; 165,65</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 6,39</t>
+          <t>-0,26; 6,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,41</t>
+          <t>-1,85; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,73</t>
+          <t>-2,59; 2,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,36</t>
+          <t>-5,14; 1,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 388,9</t>
+          <t>-18,56; 371,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 249,31</t>
+          <t>-42,4; 293,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 226,64</t>
+          <t>-63,62; 222,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,12; 391,87</t>
+          <t>-91,44; 537,74</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,51</t>
+          <t>-5,62; 3,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,51</t>
+          <t>-3,29; 3,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,38</t>
+          <t>-6,81; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,26</t>
+          <t>-3,19; 2,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 144,17</t>
+          <t>-79,45; 137,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,57; 349,63</t>
+          <t>-81,48; 279,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,46; 179,43</t>
+          <t>-81,68; 178,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 276,13</t>
+          <t>-69,8; 209,48</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,32</t>
+          <t>-1,08; 3,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,25</t>
+          <t>-1,38; 5,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,12</t>
+          <t>1,17; 7,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,18</t>
+          <t>-3,07; 1,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 362,53</t>
+          <t>-40,39; 362,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 1370,8</t>
+          <t>21,04; 1292,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-94,23; 163,35</t>
+          <t>-84,84; 287,89</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,33</t>
+          <t>-3,15; 1,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,95</t>
+          <t>-3,49; 0,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,85</t>
+          <t>-0,84; 2,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,4</t>
+          <t>-2,23; 3,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 55,06</t>
+          <t>-63,21; 51,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 44,78</t>
+          <t>-64,99; 40,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 406,98</t>
+          <t>-48,59; 398,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 127,07</t>
+          <t>-46,53; 130,09</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,72</t>
+          <t>-4,44; 0,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,09</t>
+          <t>-1,16; 2,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,91</t>
+          <t>-2,08; 2,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,76</t>
+          <t>-0,34; 4,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 18,15</t>
+          <t>-62,15; 24,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 151,01</t>
+          <t>-30,42; 126,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 82,5</t>
+          <t>-48,09; 92,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 354,99</t>
+          <t>-10,87; 315,61</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,0</t>
+          <t>-0,96; 1,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,21</t>
+          <t>-0,7; 1,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,65</t>
+          <t>-0,13; 1,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,86</t>
+          <t>-0,65; 1,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 33,87</t>
+          <t>-24,1; 36,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 43,33</t>
+          <t>-19,19; 41,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 67,6</t>
+          <t>-3,05; 71,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 70,99</t>
+          <t>-15,71; 67,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,5%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,51</t>
+          <t>-2,51; 2,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,8</t>
+          <t>-3,14; 4,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,24</t>
+          <t>-1,52; 7,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 5,08</t>
+          <t>-3,94; 4,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-99,99; 412,5</t>
+          <t>-86,39; 365,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 229,3</t>
+          <t>-59,71; 244,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 229,13</t>
+          <t>-24,41; 227,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,95; 154,3</t>
+          <t>-51,5; 171,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,64</t>
+          <t>-1,41; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,72</t>
+          <t>-4,34; 0,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,69</t>
+          <t>-1,76; 2,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,82</t>
+          <t>-1,01; 4,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 186,3</t>
+          <t>-31,12; 222,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,7; 30,55</t>
+          <t>-74,48; 26,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 244,61</t>
+          <t>-58,88; 209,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 220,02</t>
+          <t>-22,3; 193,58</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-16,65%</t>
+          <t>-16,28%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,52</t>
+          <t>-1,91; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,2</t>
+          <t>-1,44; 4,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,0</t>
+          <t>-2,58; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,57</t>
+          <t>-2,66; 1,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,63; 507,39</t>
+          <t>-71,24; 562,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 314,45</t>
+          <t>-42,02; 302,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 153,56</t>
+          <t>-60,14; 195,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,93; 165,65</t>
+          <t>-76,26; 179,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,64%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 6,56</t>
+          <t>-0,33; 6,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,29</t>
+          <t>-1,99; 4,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,58</t>
+          <t>-2,33; 2,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,48</t>
+          <t>-3,44; 2,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 371,48</t>
+          <t>-12,12; 371,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 293,24</t>
+          <t>-47,47; 283,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 222,79</t>
+          <t>-61,7; 272,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,44; 537,74</t>
+          <t>-88,59; 893,27</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 3,01</t>
+          <t>-5,16; 3,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,47</t>
+          <t>-2,81; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 3,1</t>
+          <t>-6,87; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,91</t>
+          <t>-3,24; 3,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 137,03</t>
+          <t>-78,94; 136,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-81,48; 279,28</t>
+          <t>-71,38; 412,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 178,94</t>
+          <t>-84,24; 153,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 209,48</t>
+          <t>-73,16; 228,49</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-29,14%</t>
+          <t>-28,15%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,38</t>
+          <t>-1,09; 3,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,14</t>
+          <t>-1,66; 5,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,77</t>
+          <t>1,28; 7,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,33</t>
+          <t>-3,24; 1,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 362,53</t>
+          <t>-43,54; 387,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,04; 1292,35</t>
+          <t>-3,93; 1196,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 287,89</t>
+          <t>-90,1; 167,0</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,29</t>
+          <t>-3,32; 1,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,95</t>
+          <t>-3,4; 0,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,82</t>
+          <t>-0,92; 2,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,59</t>
+          <t>-1,45; 3,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 51,07</t>
+          <t>-64,9; 56,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,99; 40,91</t>
+          <t>-64,39; 37,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 398,11</t>
+          <t>-47,76; 398,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 130,09</t>
+          <t>-27,17; 135,37</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,74</t>
+          <t>-4,37; 0,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,89</t>
+          <t>-1,14; 2,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,06</t>
+          <t>-2,23; 1,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,6</t>
+          <t>-1,39; 2,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 24,99</t>
+          <t>-62,84; 17,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 126,85</t>
+          <t>-29,29; 144,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 92,13</t>
+          <t>-48,7; 69,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 315,61</t>
+          <t>-28,61; 108,94</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,07</t>
+          <t>-0,98; 1,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,21</t>
+          <t>-0,74; 1,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,66</t>
+          <t>-0,29; 1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,79</t>
+          <t>-0,34; 1,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 36,01</t>
+          <t>-24,35; 39,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 41,98</t>
+          <t>-19,52; 41,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 71,44</t>
+          <t>-8,54; 68,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 67,38</t>
+          <t>-8,2; 59,2</t>
         </is>
       </c>
     </row>
